--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/gpt-4o-mini/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/gpt-4o-mini/stats.xlsx
@@ -980,13 +980,13 @@
         <v>2.963</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.078</v>
+        <v>1.266</v>
       </c>
       <c r="G11" t="n">
-        <v>1.148</v>
+        <v>1.341</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.891</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
-        <v>1.265</v>
+        <v>1.453</v>
       </c>
       <c r="L11" t="n">
-        <v>0.354</v>
+        <v>0.39</v>
       </c>
       <c r="M11" t="n">
-        <v>0.239</v>
+        <v>0.2151</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>2.857</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.607</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.915</v>
+        <v>1.035</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.483</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.74</v>
+        <v>0.822</v>
       </c>
       <c r="L12" t="n">
-        <v>0.217</v>
+        <v>0.234</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1355</v>
+        <v>0.1234</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1084,13 +1084,13 @@
         <v>2.355</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.552</v>
+        <v>0.579</v>
       </c>
       <c r="G13" t="n">
-        <v>0.858</v>
+        <v>0.887</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.427</v>
+        <v>0.45</v>
       </c>
       <c r="K13" t="n">
-        <v>0.681</v>
+        <v>0.716</v>
       </c>
       <c r="L13" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="M13" t="n">
-        <v>0.131</v>
+        <v>0.1107</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1136,13 +1136,13 @@
         <v>2.816</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.743</v>
+        <v>0.866</v>
       </c>
       <c r="G14" t="n">
-        <v>0.84</v>
+        <v>0.959</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.92</v>
+        <v>1.052</v>
       </c>
       <c r="L14" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1739</v>
+        <v>0.1536</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>3.12</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.891</v>
+        <v>1.13</v>
       </c>
       <c r="G15" t="n">
-        <v>1.072</v>
+        <v>1.351</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.724</v>
+        <v>0.971</v>
       </c>
       <c r="K15" t="n">
-        <v>1.06</v>
+        <v>1.302</v>
       </c>
       <c r="L15" t="n">
-        <v>0.39</v>
+        <v>0.444</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2038</v>
+        <v>0.1914</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1240,33 +1240,33 @@
         <v>0.471</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.107</v>
+        <v>0.154</v>
       </c>
       <c r="G16" t="n">
-        <v>0.488</v>
+        <v>0.708</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.063</v>
+        <v>0.111</v>
       </c>
       <c r="K16" t="n">
-        <v>0.153</v>
+        <v>0.201</v>
       </c>
       <c r="L16" t="n">
-        <v>0.158</v>
+        <v>0.18</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0289</v>
+        <v>0.0273</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>0.209</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.131</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.459</v>
+        <v>0.275</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.0001</v>
+        <v>0.0055</v>
       </c>
       <c r="J17" t="n">
-        <v>0.077</v>
+        <v>0.018</v>
       </c>
       <c r="K17" t="n">
-        <v>0.188</v>
+        <v>0.124</v>
       </c>
       <c r="L17" t="n">
-        <v>0.257</v>
+        <v>0.221</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0276</v>
+        <v>0.0185</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0001</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="18">
@@ -1344,13 +1344,13 @@
         <v>2.91</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>1.077</v>
+        <v>1.29</v>
       </c>
       <c r="G18" t="n">
-        <v>1.126</v>
+        <v>1.362</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.881</v>
+        <v>1.106</v>
       </c>
       <c r="K18" t="n">
-        <v>1.262</v>
+        <v>1.479</v>
       </c>
       <c r="L18" t="n">
-        <v>0.324</v>
+        <v>0.352</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2461</v>
+        <v>0.2228</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>3.016</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>1.242</v>
       </c>
       <c r="G19" t="n">
-        <v>1.105</v>
+        <v>1.255</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.887</v>
+        <v>1.06</v>
       </c>
       <c r="K19" t="n">
-        <v>1.281</v>
+        <v>1.446</v>
       </c>
       <c r="L19" t="n">
-        <v>0.371</v>
+        <v>0.413</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2318</v>
+        <v>0.2074</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>2.963</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>1.157</v>
+        <v>1.266</v>
       </c>
       <c r="G47" t="n">
-        <v>1.279</v>
+        <v>1.341</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="K47" t="n">
-        <v>1.34</v>
+        <v>1.453</v>
       </c>
       <c r="L47" t="n">
-        <v>0.354</v>
+        <v>0.39</v>
       </c>
       <c r="M47" t="n">
-        <v>0.239</v>
+        <v>0.2151</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>2.857</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>0.584</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.829</v>
+        <v>1.035</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.447</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>0.728</v>
+        <v>0.822</v>
       </c>
       <c r="L48" t="n">
-        <v>0.217</v>
+        <v>0.234</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1355</v>
+        <v>0.1234</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>2.355</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="G49" t="n">
-        <v>0.829</v>
+        <v>0.887</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.439</v>
+        <v>0.45</v>
       </c>
       <c r="K49" t="n">
-        <v>0.704</v>
+        <v>0.716</v>
       </c>
       <c r="L49" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="M49" t="n">
-        <v>0.131</v>
+        <v>0.1107</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>2.816</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.806</v>
+        <v>0.866</v>
       </c>
       <c r="G50" t="n">
-        <v>0.861</v>
+        <v>0.959</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.639</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>0.998</v>
+        <v>1.052</v>
       </c>
       <c r="L50" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1739</v>
+        <v>0.1536</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>3.12</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>0.964</v>
+        <v>1.13</v>
       </c>
       <c r="G51" t="n">
-        <v>1.188</v>
+        <v>1.351</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.971</v>
       </c>
       <c r="K51" t="n">
-        <v>1.122</v>
+        <v>1.302</v>
       </c>
       <c r="L51" t="n">
-        <v>0.39</v>
+        <v>0.444</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2038</v>
+        <v>0.1914</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>0.471</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>0.143</v>
+        <v>0.154</v>
       </c>
       <c r="G52" t="n">
-        <v>0.629</v>
+        <v>0.708</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3129,16 +3129,16 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="K52" t="n">
-        <v>0.192</v>
+        <v>0.201</v>
       </c>
       <c r="L52" t="n">
-        <v>0.158</v>
+        <v>0.18</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0289</v>
+        <v>0.0273</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>0.209</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>0.096</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.378</v>
+        <v>0.275</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3178,22 +3178,22 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.0003</v>
+        <v>0.0055</v>
       </c>
       <c r="J53" t="n">
-        <v>0.046</v>
+        <v>0.018</v>
       </c>
       <c r="K53" t="n">
-        <v>0.146</v>
+        <v>0.124</v>
       </c>
       <c r="L53" t="n">
-        <v>0.257</v>
+        <v>0.221</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0276</v>
+        <v>0.0185</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0003</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="54">
@@ -3216,13 +3216,13 @@
         <v>2.91</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="G54" t="n">
-        <v>1.312</v>
+        <v>1.362</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.015</v>
+        <v>1.106</v>
       </c>
       <c r="K54" t="n">
-        <v>1.375</v>
+        <v>1.479</v>
       </c>
       <c r="L54" t="n">
-        <v>0.324</v>
+        <v>0.352</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2461</v>
+        <v>0.2228</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>3.016</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>1.124</v>
+        <v>1.242</v>
       </c>
       <c r="G55" t="n">
-        <v>1.178</v>
+        <v>1.255</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.948</v>
+        <v>1.06</v>
       </c>
       <c r="K55" t="n">
-        <v>1.313</v>
+        <v>1.446</v>
       </c>
       <c r="L55" t="n">
-        <v>0.371</v>
+        <v>0.413</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2318</v>
+        <v>0.2074</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>192.5974</v>
+        <v>280.4418</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4012</v>
+        <v>0.4869</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>96</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>99.3586</v>
+        <v>139.5349</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.207</v>
+        <v>0.2422</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>96</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>105.4563</v>
+        <v>126.8675</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2197</v>
+        <v>0.2203</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>96</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>107.8074</v>
+        <v>144.0708</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2246</v>
+        <v>0.2501</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>96</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>166.4542</v>
+        <v>239.9247</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3468</v>
+        <v>0.4165</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>96</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>58.5096</v>
+        <v>75.2861</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1219</v>
+        <v>0.1307</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
         <v>96</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>46.531</v>
+        <v>49.7217</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0969</v>
+        <v>0.0863</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>96</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>206.1555</v>
+        <v>279.6324</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4295</v>
+        <v>0.4855</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>96</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>182.9451</v>
+        <v>268.6589</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3811</v>
+        <v>0.4664</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>96</v>
@@ -5270,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5788,32 +5788,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2632</v>
+        <v>1.2658</v>
       </c>
       <c r="E17" t="n">
-        <v>0.269</v>
+        <v>1.3408</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0814</v>
+        <v>1.0904</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4545</v>
+        <v>1.4531</v>
       </c>
     </row>
     <row r="18">
@@ -5823,28 +5823,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4659</v>
+        <v>0.2632</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4587</v>
+        <v>0.269</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.0352</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0352</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2651</v>
+        <v>0.0814</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6732</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="19">
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>96</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8145</v>
+        <v>0.4659</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8427</v>
+        <v>0.4587</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6185</v>
+        <v>0.2651</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0041</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="20">
@@ -5885,16 +5885,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0072</v>
+        <v>0.8145</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0782</v>
+        <v>0.8427</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -5903,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8208</v>
+        <v>0.6185</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1967</v>
+        <v>1.0041</v>
       </c>
     </row>
     <row r="21">
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0141</v>
+        <v>1.0072</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0532</v>
+        <v>1.0782</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8208</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2057</v>
+        <v>1.1967</v>
       </c>
     </row>
     <row r="22">
@@ -5947,16 +5947,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1536</v>
+        <v>1.0141</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2035</v>
+        <v>1.0532</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -5965,10 +5965,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3494</v>
+        <v>1.2057</v>
       </c>
     </row>
     <row r="23">
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>96</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1287</v>
+        <v>1.1536</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1216</v>
+        <v>1.2035</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9314</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3231</v>
+        <v>1.3494</v>
       </c>
     </row>
     <row r="24">
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>96</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2203</v>
+        <v>1.1287</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2504</v>
+        <v>1.1216</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.03</v>
+        <v>0.9314</v>
       </c>
       <c r="I24" t="n">
-        <v>1.424</v>
+        <v>1.3231</v>
       </c>
     </row>
     <row r="25">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>96</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2381</v>
+        <v>1.2203</v>
       </c>
       <c r="E25" t="n">
-        <v>1.31</v>
+        <v>1.2504</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0483</v>
+        <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4242</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="26">
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
         <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2594</v>
+        <v>1.2381</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4288</v>
+        <v>1.31</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -6089,41 +6089,41 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0859</v>
+        <v>1.0483</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4336</v>
+        <v>1.4242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1775</v>
+        <v>1.2594</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1629</v>
+        <v>1.4288</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1293</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1293</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0378</v>
+        <v>1.0859</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3901</v>
+        <v>1.4336</v>
       </c>
     </row>
     <row r="28">
@@ -6133,28 +6133,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3048</v>
+        <v>0.1775</v>
       </c>
       <c r="E28" t="n">
-        <v>0.275</v>
+        <v>0.1629</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0185</v>
+        <v>0.1293</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0369</v>
+        <v>0.1293</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0911</v>
+        <v>-0.0378</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5242</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="29">
@@ -6164,28 +6164,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>0.671</v>
+        <v>0.3048</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6714</v>
+        <v>0.275</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0185</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4645</v>
+        <v>0.0911</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8743</v>
+        <v>0.5242</v>
       </c>
     </row>
     <row r="30">
@@ -6195,16 +6195,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8847</v>
+        <v>0.671</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8811</v>
+        <v>0.6714</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -6213,10 +6213,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6894</v>
+        <v>0.4645</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0835</v>
+        <v>0.8743</v>
       </c>
     </row>
     <row r="31">
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>1.0133</v>
+        <v>0.8847</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0351</v>
+        <v>0.8811</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8158</v>
+        <v>0.6894</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2056</v>
+        <v>1.0835</v>
       </c>
     </row>
     <row r="32">
@@ -6257,16 +6257,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8939</v>
+        <v>1.0133</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8753</v>
+        <v>1.0351</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.8158</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0944</v>
+        <v>1.2056</v>
       </c>
     </row>
     <row r="33">
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
         <v>96</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0822</v>
+        <v>0.8939</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0674</v>
+        <v>0.8753</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -6306,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8802</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2809</v>
+        <v>1.0944</v>
       </c>
     </row>
     <row r="34">
@@ -6319,16 +6319,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
         <v>96</v>
       </c>
       <c r="D34" t="n">
-        <v>1.1406</v>
+        <v>1.0822</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1234</v>
+        <v>1.0674</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9434</v>
+        <v>0.8802</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3489</v>
+        <v>1.2809</v>
       </c>
     </row>
     <row r="35">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" t="n">
         <v>96</v>
       </c>
       <c r="D35" t="n">
-        <v>1.1939</v>
+        <v>1.1406</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1334</v>
+        <v>1.1234</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9928</v>
+        <v>0.9434</v>
       </c>
       <c r="I35" t="n">
-        <v>1.4036</v>
+        <v>1.3489</v>
       </c>
     </row>
     <row r="36">
@@ -6381,27 +6381,58 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
         <v>96</v>
       </c>
       <c r="D36" t="n">
+        <v>1.1939</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.1334</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.4036</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" t="n">
+        <v>96</v>
+      </c>
+      <c r="D37" t="n">
         <v>1.3035</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>1.3532</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.1051</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>1.4951</v>
       </c>
     </row>
@@ -6679,16 +6710,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3538</v>
+        <v>0.3896</v>
       </c>
       <c r="D11" t="n">
-        <v>0.239</v>
+        <v>0.2151</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -6703,16 +6734,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2166</v>
+        <v>0.2339</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1355</v>
+        <v>0.1234</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -6727,16 +6758,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1994</v>
+        <v>0.1984</v>
       </c>
       <c r="D13" t="n">
-        <v>0.131</v>
+        <v>0.1107</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -6751,16 +6782,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2026</v>
+        <v>0.2125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1739</v>
+        <v>0.1536</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -6775,16 +6806,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3904</v>
+        <v>0.4438</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2038</v>
+        <v>0.1914</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -6799,16 +6830,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1582</v>
+        <v>0.18</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0289</v>
+        <v>0.0273</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -6823,16 +6854,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2573</v>
+        <v>0.2212</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0276</v>
+        <v>0.0185</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -6847,16 +6878,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3243</v>
+        <v>0.3522</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2461</v>
+        <v>0.2228</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -6871,16 +6902,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.371</v>
+        <v>0.4133</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2318</v>
+        <v>0.2074</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -7358,7 +7389,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="4">

--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/gpt-4o-mini/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/gpt-4o-mini/stats.xlsx
@@ -980,13 +980,13 @@
         <v>2.963</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.266</v>
+        <v>1.554</v>
       </c>
       <c r="G11" t="n">
-        <v>1.341</v>
+        <v>1.518</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>1.354</v>
       </c>
       <c r="K11" t="n">
-        <v>1.453</v>
+        <v>1.759</v>
       </c>
       <c r="L11" t="n">
-        <v>0.39</v>
+        <v>0.465</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2151</v>
+        <v>0.1444</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>2.857</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.872</v>
       </c>
       <c r="G12" t="n">
-        <v>1.035</v>
+        <v>1.305</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="K12" t="n">
-        <v>0.822</v>
+        <v>1.008</v>
       </c>
       <c r="L12" t="n">
-        <v>0.234</v>
+        <v>0.266</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1234</v>
+        <v>0.0843</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1084,13 +1084,13 @@
         <v>2.355</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.579</v>
+        <v>0.707</v>
       </c>
       <c r="G13" t="n">
-        <v>0.887</v>
+        <v>0.951</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.45</v>
+        <v>0.556</v>
       </c>
       <c r="K13" t="n">
-        <v>0.716</v>
+        <v>0.855</v>
       </c>
       <c r="L13" t="n">
-        <v>0.198</v>
+        <v>0.191</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1107</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1136,13 +1136,13 @@
         <v>2.816</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.866</v>
+        <v>1.016</v>
       </c>
       <c r="G14" t="n">
-        <v>0.959</v>
+        <v>1.075</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="K14" t="n">
-        <v>1.052</v>
+        <v>1.205</v>
       </c>
       <c r="L14" t="n">
-        <v>0.213</v>
+        <v>0.225</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1536</v>
+        <v>0.0961</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>3.12</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>1.13</v>
+        <v>1.417</v>
       </c>
       <c r="G15" t="n">
-        <v>1.351</v>
+        <v>1.629</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.971</v>
+        <v>1.245</v>
       </c>
       <c r="K15" t="n">
-        <v>1.302</v>
+        <v>1.591</v>
       </c>
       <c r="L15" t="n">
-        <v>0.444</v>
+        <v>0.554</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1914</v>
+        <v>0.1391</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1240,33 +1240,33 @@
         <v>0.471</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="G16" t="n">
-        <v>0.708</v>
+        <v>0.859</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.111</v>
+        <v>0.166</v>
       </c>
       <c r="K16" t="n">
-        <v>0.201</v>
+        <v>0.264</v>
       </c>
       <c r="L16" t="n">
-        <v>0.18</v>
+        <v>0.238</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0273</v>
+        <v>0.0217</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1292,36 +1292,36 @@
         <v>0.209</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.275</v>
+        <v>0.006</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.0055</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.018</v>
+        <v>-0.043</v>
       </c>
       <c r="K17" t="n">
-        <v>0.124</v>
+        <v>0.048</v>
       </c>
       <c r="L17" t="n">
-        <v>0.221</v>
+        <v>-0.008</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0185</v>
+        <v>-0.0027</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0055</v>
+        <v>0.7112000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1344,13 +1344,13 @@
         <v>2.91</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>1.29</v>
+        <v>1.554</v>
       </c>
       <c r="G18" t="n">
-        <v>1.362</v>
+        <v>1.462</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.106</v>
+        <v>1.342</v>
       </c>
       <c r="K18" t="n">
-        <v>1.479</v>
+        <v>1.769</v>
       </c>
       <c r="L18" t="n">
-        <v>0.352</v>
+        <v>0.39</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2228</v>
+        <v>0.1466</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>3.016</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.242</v>
+        <v>1.554</v>
       </c>
       <c r="G19" t="n">
-        <v>1.255</v>
+        <v>1.505</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.06</v>
+        <v>1.349</v>
       </c>
       <c r="K19" t="n">
-        <v>1.446</v>
+        <v>1.76</v>
       </c>
       <c r="L19" t="n">
-        <v>0.413</v>
+        <v>0.522</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2074</v>
+        <v>0.1422</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>2.963</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>1.266</v>
+        <v>1.554</v>
       </c>
       <c r="G47" t="n">
-        <v>1.341</v>
+        <v>1.518</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09</v>
+        <v>1.354</v>
       </c>
       <c r="K47" t="n">
-        <v>1.453</v>
+        <v>1.759</v>
       </c>
       <c r="L47" t="n">
-        <v>0.39</v>
+        <v>0.465</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2151</v>
+        <v>0.1444</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>2.857</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.872</v>
       </c>
       <c r="G48" t="n">
-        <v>1.035</v>
+        <v>1.305</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="K48" t="n">
-        <v>0.822</v>
+        <v>1.008</v>
       </c>
       <c r="L48" t="n">
-        <v>0.234</v>
+        <v>0.266</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1234</v>
+        <v>0.0843</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>2.355</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>0.579</v>
+        <v>0.707</v>
       </c>
       <c r="G49" t="n">
-        <v>0.887</v>
+        <v>0.951</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.45</v>
+        <v>0.556</v>
       </c>
       <c r="K49" t="n">
-        <v>0.716</v>
+        <v>0.855</v>
       </c>
       <c r="L49" t="n">
-        <v>0.198</v>
+        <v>0.191</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1107</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>2.816</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>0.866</v>
+        <v>1.016</v>
       </c>
       <c r="G50" t="n">
-        <v>0.959</v>
+        <v>1.075</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="K50" t="n">
-        <v>1.052</v>
+        <v>1.205</v>
       </c>
       <c r="L50" t="n">
-        <v>0.213</v>
+        <v>0.225</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1536</v>
+        <v>0.0961</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>3.12</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>1.13</v>
+        <v>1.417</v>
       </c>
       <c r="G51" t="n">
-        <v>1.351</v>
+        <v>1.629</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.971</v>
+        <v>1.245</v>
       </c>
       <c r="K51" t="n">
-        <v>1.302</v>
+        <v>1.591</v>
       </c>
       <c r="L51" t="n">
-        <v>0.444</v>
+        <v>0.554</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1914</v>
+        <v>0.1391</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3112,33 +3112,33 @@
         <v>0.471</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="G52" t="n">
-        <v>0.708</v>
+        <v>0.859</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.111</v>
+        <v>0.166</v>
       </c>
       <c r="K52" t="n">
-        <v>0.201</v>
+        <v>0.264</v>
       </c>
       <c r="L52" t="n">
-        <v>0.18</v>
+        <v>0.238</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0273</v>
+        <v>0.0217</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3164,36 +3164,36 @@
         <v>0.209</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="G53" t="n">
-        <v>0.275</v>
+        <v>0.006</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.0055</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>0.018</v>
+        <v>-0.043</v>
       </c>
       <c r="K53" t="n">
-        <v>0.124</v>
+        <v>0.048</v>
       </c>
       <c r="L53" t="n">
-        <v>0.221</v>
+        <v>-0.008</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0185</v>
+        <v>-0.0027</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0055</v>
+        <v>0.7112000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3216,13 +3216,13 @@
         <v>2.91</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>1.29</v>
+        <v>1.554</v>
       </c>
       <c r="G54" t="n">
-        <v>1.362</v>
+        <v>1.462</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.106</v>
+        <v>1.342</v>
       </c>
       <c r="K54" t="n">
-        <v>1.479</v>
+        <v>1.769</v>
       </c>
       <c r="L54" t="n">
-        <v>0.352</v>
+        <v>0.39</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2228</v>
+        <v>0.1466</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>3.016</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>1.242</v>
+        <v>1.554</v>
       </c>
       <c r="G55" t="n">
-        <v>1.255</v>
+        <v>1.505</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1.06</v>
+        <v>1.349</v>
       </c>
       <c r="K55" t="n">
-        <v>1.446</v>
+        <v>1.76</v>
       </c>
       <c r="L55" t="n">
-        <v>0.413</v>
+        <v>0.522</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2074</v>
+        <v>0.1422</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>280.4418</v>
+        <v>586.801</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4869</v>
+        <v>0.6113</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>96</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>139.5349</v>
+        <v>320.4206</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2422</v>
+        <v>0.3338</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>96</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>126.8675</v>
+        <v>211.8177</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2203</v>
+        <v>0.2206</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>96</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>144.0708</v>
+        <v>273.1434</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2501</v>
+        <v>0.2845</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
         <v>96</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>239.9247</v>
+        <v>521.1101</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4165</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>96</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>75.2861</v>
+        <v>191.8442</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1307</v>
+        <v>0.1998</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
         <v>96</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49.7217</v>
+        <v>74.1716</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0863</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
         <v>96</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>279.6324</v>
+        <v>501.4438</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4855</v>
+        <v>0.5223</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
         <v>96</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>268.6589</v>
+        <v>587.2369</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4664</v>
+        <v>0.6117</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
         <v>96</v>
@@ -5270,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,51 +5819,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2632</v>
+        <v>1.3069</v>
       </c>
       <c r="E18" t="n">
-        <v>0.269</v>
+        <v>1.3861</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0814</v>
+        <v>1.1239</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4545</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>96</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4659</v>
+        <v>1.2912</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4587</v>
+        <v>1.2957</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -5872,29 +5872,29 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2651</v>
+        <v>1.0964</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6732</v>
+        <v>1.4843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8145</v>
+        <v>1.4913</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8427</v>
+        <v>1.4425</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -5903,29 +5903,29 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6185</v>
+        <v>1.2906</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0041</v>
+        <v>1.6924</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0072</v>
+        <v>1.554</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0782</v>
+        <v>1.518</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8208</v>
+        <v>1.354</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1967</v>
+        <v>1.7593</v>
       </c>
     </row>
     <row r="22">
@@ -5947,28 +5947,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0141</v>
+        <v>0.2632</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0532</v>
+        <v>0.269</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.0352</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0352</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2057</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="23">
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>96</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1536</v>
+        <v>0.4659</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2035</v>
+        <v>0.4587</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.2651</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3494</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="24">
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>96</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1287</v>
+        <v>0.8145</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1216</v>
+        <v>0.8427</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9314</v>
+        <v>0.6185</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3231</v>
+        <v>1.0041</v>
       </c>
     </row>
     <row r="25">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>96</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2203</v>
+        <v>1.0072</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2504</v>
+        <v>1.0782</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.03</v>
+        <v>0.8208</v>
       </c>
       <c r="I25" t="n">
-        <v>1.424</v>
+        <v>1.1967</v>
       </c>
     </row>
     <row r="26">
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
         <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2381</v>
+        <v>1.0141</v>
       </c>
       <c r="E26" t="n">
-        <v>1.31</v>
+        <v>1.0532</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -6089,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0483</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4242</v>
+        <v>1.2057</v>
       </c>
     </row>
     <row r="27">
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2594</v>
+        <v>1.1536</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4288</v>
+        <v>1.2035</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -6120,91 +6120,91 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0859</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4336</v>
+        <v>1.3494</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1775</v>
+        <v>1.1287</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1629</v>
+        <v>1.1216</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1293</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1293</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0378</v>
+        <v>0.9314</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3901</v>
+        <v>1.3231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3048</v>
+        <v>1.2203</v>
       </c>
       <c r="E29" t="n">
-        <v>0.275</v>
+        <v>1.2504</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0185</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0369</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0911</v>
+        <v>1.03</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5242</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>0.671</v>
+        <v>1.2381</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6714</v>
+        <v>1.31</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -6213,29 +6213,29 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4645</v>
+        <v>1.0483</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8743</v>
+        <v>1.4242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8847</v>
+        <v>1.2594</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8811</v>
+        <v>1.4288</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6894</v>
+        <v>1.0859</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0835</v>
+        <v>1.4336</v>
       </c>
     </row>
     <row r="32">
@@ -6257,28 +6257,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0133</v>
+        <v>0.1775</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0351</v>
+        <v>0.1629</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.1293</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.1293</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8158</v>
+        <v>-0.0378</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2056</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="33">
@@ -6288,28 +6288,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>96</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8939</v>
+        <v>0.3048</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8753</v>
+        <v>0.275</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.0185</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.0911</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0944</v>
+        <v>0.5242</v>
       </c>
     </row>
     <row r="34">
@@ -6319,16 +6319,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>96</v>
       </c>
       <c r="D34" t="n">
-        <v>1.0822</v>
+        <v>0.671</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0674</v>
+        <v>0.6714</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8802</v>
+        <v>0.4645</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2809</v>
+        <v>0.8743</v>
       </c>
     </row>
     <row r="35">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>96</v>
       </c>
       <c r="D35" t="n">
-        <v>1.1406</v>
+        <v>0.8847</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1234</v>
+        <v>0.8811</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9434</v>
+        <v>0.6894</v>
       </c>
       <c r="I35" t="n">
-        <v>1.3489</v>
+        <v>1.0835</v>
       </c>
     </row>
     <row r="36">
@@ -6381,16 +6381,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>96</v>
       </c>
       <c r="D36" t="n">
-        <v>1.1939</v>
+        <v>1.0133</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1334</v>
+        <v>1.0351</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9928</v>
+        <v>0.8158</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4036</v>
+        <v>1.2056</v>
       </c>
     </row>
     <row r="37">
@@ -6412,27 +6412,151 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
         <v>96</v>
       </c>
       <c r="D37" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8753</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.0944</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>96</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.0822</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.0674</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.2809</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>96</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.1406</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.1234</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.3489</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>96</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.1939</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.1334</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.4036</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" t="n">
+        <v>96</v>
+      </c>
+      <c r="D41" t="n">
         <v>1.3035</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E41" t="n">
         <v>1.3532</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>1.1051</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I41" t="n">
         <v>1.4951</v>
       </c>
     </row>
@@ -6710,16 +6834,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3896</v>
+        <v>0.465</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2151</v>
+        <v>0.1444</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -6734,16 +6858,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2339</v>
+        <v>0.2659</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1234</v>
+        <v>0.0843</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -6758,16 +6882,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1984</v>
+        <v>0.1914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1107</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -6782,16 +6906,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2125</v>
+        <v>0.2248</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1536</v>
+        <v>0.0961</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -6806,16 +6930,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4438</v>
+        <v>0.5535</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1914</v>
+        <v>0.1391</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -6830,16 +6954,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.18</v>
+        <v>0.2384</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0273</v>
+        <v>0.0217</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -6854,16 +6978,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2212</v>
+        <v>-0.0077</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0185</v>
+        <v>-0.0027</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -6878,16 +7002,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3522</v>
+        <v>0.3901</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2228</v>
+        <v>0.1466</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -6902,16 +7026,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4133</v>
+        <v>0.5225</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2074</v>
+        <v>0.1422</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -7389,7 +7513,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="4">
